--- a/server/master-excel-files/General_CHEMISTRY_Grade 8.xlsx
+++ b/server/master-excel-files/General_CHEMISTRY_Grade 8.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\Teachers year plan\CHEMISTRY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\Teachers year plan\CHEMISTRY\SUMERU\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -78,9 +78,6 @@
     <t>SECTION-6</t>
   </si>
   <si>
-    <t>IIT  SYLLABUS</t>
-  </si>
-  <si>
     <t>Base line test</t>
   </si>
   <si>
@@ -100,6 +97,9 @@
   </si>
   <si>
     <t>Atomic Structure</t>
+  </si>
+  <si>
+    <t>IIT SYLLABUS</t>
   </si>
 </sst>
 </file>
@@ -584,7 +584,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>13</v>
@@ -626,7 +626,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -657,13 +657,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>5</v>
@@ -692,11 +692,11 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>5</v>
@@ -725,13 +725,13 @@
         <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>5</v>

--- a/server/master-excel-files/General_CHEMISTRY_Grade 8.xlsx
+++ b/server/master-excel-files/General_CHEMISTRY_Grade 8.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\Teachers year plan\CHEMISTRY\SUMERU\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\teacher-year-plan-app\server\master-excel-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -800,9 +800,12 @@
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="H8:I42 E1:K1 E3:K7">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="E1:K1 H8:I40">
       <formula1>"Not Started,In Progress,Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="E3:K7">
+      <formula1>"Not Assigned,In Progress,Completed"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
